--- a/etf_holdings/2026-09-12_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-12_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.63%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.63%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.19%5365</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.19%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5365</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.86%4585</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.86%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4585</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.6%3370</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.6%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3370</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.71%977</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.71%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>977</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.49%2310</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.49%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2310</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%5620</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5620</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.43%5765</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.43%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5765</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.9%544</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.9%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>544</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.4%140.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.4%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>140.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.07%1885</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.07%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1885</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.28%1620</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.28%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1620</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.92%618</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.92%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>618</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.93%1080</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.93%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1080</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:39</t>
+          <t>2026-09-12 21:05:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.85%1875</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.85%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1875</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:46</t>
+          <t>2026-09-12 21:05:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:47</t>
+          <t>2026-09-12 21:05:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:48</t>
+          <t>2026-09-12 21:05:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:48</t>
+          <t>2026-09-12 21:05:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:48</t>
+          <t>2026-09-12 21:05:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:48</t>
+          <t>2026-09-12 21:05:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:48</t>
+          <t>2026-09-12 21:05:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-12 20:54:48</t>
+          <t>2026-09-12 21:05:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-12_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-12_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:31</t>
+          <t>2026-09-12 21:12:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:32</t>
+          <t>2026-09-12 21:12:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:34</t>
+          <t>2026-09-12 21:12:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:35</t>
+          <t>2026-09-12 21:12:19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:35</t>
+          <t>2026-09-12 21:12:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:35</t>
+          <t>2026-09-12 21:12:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:35</t>
+          <t>2026-09-12 21:12:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:35</t>
+          <t>2026-09-12 21:12:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-12 21:05:35</t>
+          <t>2026-09-12 21:12:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
